--- a/ams/cases/ieee14/ieee14_uced.xlsx
+++ b/ams/cases/ieee14/ieee14_uced.xlsx
@@ -17,10 +17,10 @@
     <sheet name="Area" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="GCost" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Zone" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="EDTSlot" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="EDSlot" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="EDSlotLoad" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="EDSlotGen" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="UCTSlot" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="UCSlot" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="UCSlotLoad" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="SFR" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="SFRCost" sheetId="17" state="visible" r:id="rId17"/>

--- a/ams/cases/ieee14/ieee14_uced.xlsx
+++ b/ams/cases/ieee14/ieee14_uced.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Load factor in EDTSlot and UCTSlot sourced from ISO-NE day-ahead cleared hourly load on 2022 June 29</t>
+          <t>Load factor in EDSlotLoad and UCSlotLoad sourced from ISO-NE day-ahead cleared hourly load on 2022 June 29</t>
         </is>
       </c>
     </row>
